--- a/order_generation/PO_excel_export/factory-4.xlsx
+++ b/order_generation/PO_excel_export/factory-4.xlsx
@@ -890,24 +890,66 @@
       <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
-      <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>圆形品牌logo贴纸</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr">
+        <is>
+          <t>散货</t>
+        </is>
+      </c>
       <c r="H8" s="20" t="n"/>
     </row>
-    <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
+    <row r="9" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>ST1122-4</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>[图片未找到] [图片未找到]</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>猪鬃木纹天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F9" s="29">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="29" t="inlineStr"/>
       <c r="H9" s="20" t="n"/>
     </row>
     <row r="10" ht="17.25" customFormat="1" customHeight="1" s="3">
